--- a/投手能力データ_最新.xlsx
+++ b/投手能力データ_最新.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30513"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4C6801F-3CDA-A144-9215-F200DE59CCD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C06BD7E3-A531-AA4A-AD36-51A8C492E3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="371">
   <si>
     <t>選手名</t>
   </si>
@@ -150,9 +150,6 @@
     <t>高橋光成</t>
   </si>
   <si>
-    <t>渡辺勇太朗</t>
-  </si>
-  <si>
     <t>井上温大</t>
   </si>
   <si>
@@ -336,9 +333,6 @@
     <t>フォーシーム:C / シンカー:A / カーブ:D / チェンジアップ:F</t>
   </si>
   <si>
-    <t>フォーシーム:D / カットボール:C / スライダー:C / フォーク:B / カーブ:F</t>
-  </si>
-  <si>
     <t>フォーシーム:D / カットボール:E / フォーク:E / カーブ:B / スライダー:B</t>
   </si>
   <si>
@@ -666,9 +660,6 @@
     <t>篠原響</t>
   </si>
   <si>
-    <t>フォーシーム:C / スライダー:D / チェンジアップ:C</t>
-  </si>
-  <si>
     <t>ウォルターズ</t>
   </si>
   <si>
@@ -714,9 +705,6 @@
     <t>上原健太</t>
   </si>
   <si>
-    <t>フォーシーム:E / カットボール:C / フォーク:F / シンカー:A / スライダー:A</t>
-  </si>
-  <si>
     <t>豆田泰志</t>
   </si>
   <si>
@@ -825,9 +813,6 @@
     <t>ツーシーム:B / カーブ:B / スライダー:C / チェンジアップ:C / カットボール:F</t>
   </si>
   <si>
-    <t>ツーシーム:E / スライダー:B / チェンジアップ:B / フォーク:E / シンカー:C</t>
-  </si>
-  <si>
     <t>フォーシーム:A / カットボール:C / フォーク:E / カーブ:D / シンカー:F</t>
   </si>
   <si>
@@ -882,9 +867,6 @@
     <t>フォーシーム:E / フォーク:C / カットボール:B / カーブ:E</t>
   </si>
   <si>
-    <t>フォーシーム:A / カットボール:C / スライダー:A / チェンジアップ:F / フォーク:D</t>
-  </si>
-  <si>
     <t>フォーシーム:C / チェンジアップ:F / カットボール:C / カーブ:D / シンカー:C</t>
   </si>
   <si>
@@ -981,9 +963,6 @@
     <t>フォーシーム:B / フォーク:F / スライダー:C / カットボール:D</t>
   </si>
   <si>
-    <t>フォーシーム:D / チェンジアップ:B / スライダー:C / ツーシーム:E / カーブ:E</t>
-  </si>
-  <si>
     <t>フォーシーム:B / フォーク:B / カットボール:B</t>
   </si>
   <si>
@@ -999,9 +978,6 @@
     <t>フォーシーム:B / スライダー:C / フォーク:F / チェンジアップ:C / シュート:E</t>
   </si>
   <si>
-    <t>フォーシーム:B / シンカー:F / スライダー:F / フォーク:F / カーブ:E</t>
-  </si>
-  <si>
     <t>フォーシーム:B / カットボール:B / チェンジアップ:D / カーブ:D</t>
   </si>
   <si>
@@ -1086,18 +1062,9 @@
     <t>フォーシーム:D / スライダー:B / チェンジアップ:C / フォーク:F / カットボール:D</t>
   </si>
   <si>
-    <t>フォーシーム:D / カーブ:A / フォーク:B / チェンジアップ:C / カットボール:E</t>
-  </si>
-  <si>
-    <t>フォーシーム:B / シンカー:S / スライダー:E / フォーク:E / カットボール:D</t>
-  </si>
-  <si>
     <t>スライダー:B / フォーシーム:B / シンカー:E / カーブ:E / フォーク:D</t>
   </si>
   <si>
-    <t>フォーシーム:B / フォーク:C / カットボール:D / カーブ:D / チェンジアップ:D</t>
-  </si>
-  <si>
     <t>フォーシーム:E / フォーク:B / カットボール:E / スライダー:F</t>
   </si>
   <si>
@@ -1141,6 +1108,39 @@
   </si>
   <si>
     <t>フォーシーム:F / フォーク:E / スライダー:C / シンカー:F / カーブ:E</t>
+  </si>
+  <si>
+    <t>フォーシーム:D / カットボール:C / スライダー:C / フォーク:C / カーブ:F</t>
+  </si>
+  <si>
+    <t>ツーシーム:F / スライダー:D / チェンジアップ:C / フォーク:E / シンカー:E</t>
+  </si>
+  <si>
+    <t>フォーシーム:B / フォーク:C / カットボール:D / カーブ:D</t>
+  </si>
+  <si>
+    <t>フォーシーム:E / カットボール:C / フォーク:F / シンカー:D / スライダー:C</t>
+  </si>
+  <si>
+    <t>フォーシーム:B / チェンジアップ:B / スライダー:C / ツーシーム:E / カーブ:E</t>
+  </si>
+  <si>
+    <t>フォーシーム:C / カーブ:A / フォーク:B / チェンジアップ:C / カットボール:E</t>
+  </si>
+  <si>
+    <t>渡邉勇太朗</t>
+  </si>
+  <si>
+    <t>フォーシーム:A / カットボール:A / スライダー:B / チェンジアップ:B / フォーク:D</t>
+  </si>
+  <si>
+    <t>フォーシーム:B / シンカー:S / スライダー:E / フォーク:E / カットボール:B</t>
+  </si>
+  <si>
+    <t>フォーシーム:B / スライダー:C / チェンジアップ:B</t>
+  </si>
+  <si>
+    <t>フォーシーム:D / シンカー:F / スライダー:F / フォーク:F / カーブ:E</t>
   </si>
 </sst>
 </file>
@@ -1554,7 +1554,7 @@
         <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -1571,7 +1571,7 @@
         <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1588,7 +1588,7 @@
         <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1605,7 +1605,7 @@
         <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1622,7 +1622,7 @@
         <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1639,7 +1639,7 @@
         <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1656,7 +1656,7 @@
         <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1673,7 +1673,7 @@
         <v>76</v>
       </c>
       <c r="E9" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -1690,7 +1690,7 @@
         <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -1724,7 +1724,7 @@
         <v>76</v>
       </c>
       <c r="E12" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -1735,13 +1735,13 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D13">
         <v>75</v>
       </c>
       <c r="E13" t="s">
-        <v>283</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -1758,7 +1758,7 @@
         <v>74</v>
       </c>
       <c r="E14" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -1769,13 +1769,13 @@
         <v>6</v>
       </c>
       <c r="C15">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -1792,7 +1792,7 @@
         <v>75</v>
       </c>
       <c r="E16" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -1809,7 +1809,7 @@
         <v>76</v>
       </c>
       <c r="E17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -1826,7 +1826,7 @@
         <v>76</v>
       </c>
       <c r="E18" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -1843,7 +1843,7 @@
         <v>70</v>
       </c>
       <c r="E19" t="s">
-        <v>264</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -1854,13 +1854,13 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D20">
         <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>101</v>
+        <v>359</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -1877,7 +1877,7 @@
         <v>77</v>
       </c>
       <c r="E21" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -1894,7 +1894,7 @@
         <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -1911,12 +1911,12 @@
         <v>76</v>
       </c>
       <c r="E23" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>365</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
@@ -1928,15 +1928,15 @@
         <v>76</v>
       </c>
       <c r="E24" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25">
         <v>70</v>
@@ -1945,12 +1945,12 @@
         <v>75</v>
       </c>
       <c r="E25" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
         <v>33</v>
@@ -1962,12 +1962,12 @@
         <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
@@ -1979,12 +1979,12 @@
         <v>73</v>
       </c>
       <c r="E27" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
@@ -1996,12 +1996,12 @@
         <v>77</v>
       </c>
       <c r="E28" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s">
         <v>16</v>
@@ -2013,15 +2013,15 @@
         <v>77</v>
       </c>
       <c r="E29" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C30">
         <v>60</v>
@@ -2030,12 +2030,12 @@
         <v>72</v>
       </c>
       <c r="E30" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
@@ -2047,12 +2047,12 @@
         <v>59</v>
       </c>
       <c r="E31" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
@@ -2064,12 +2064,12 @@
         <v>69</v>
       </c>
       <c r="E32" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B33" t="s">
         <v>33</v>
@@ -2081,12 +2081,12 @@
         <v>70</v>
       </c>
       <c r="E33" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B34" t="s">
         <v>22</v>
@@ -2098,12 +2098,12 @@
         <v>70</v>
       </c>
       <c r="E34" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
@@ -2115,12 +2115,12 @@
         <v>76</v>
       </c>
       <c r="E35" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
@@ -2132,12 +2132,12 @@
         <v>58</v>
       </c>
       <c r="E36" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B37" t="s">
         <v>19</v>
@@ -2149,12 +2149,12 @@
         <v>72</v>
       </c>
       <c r="E37" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B38" t="s">
         <v>27</v>
@@ -2166,12 +2166,12 @@
         <v>72</v>
       </c>
       <c r="E38" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B39" t="s">
         <v>22</v>
@@ -2183,12 +2183,12 @@
         <v>65</v>
       </c>
       <c r="E39" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B40" t="s">
         <v>37</v>
@@ -2200,12 +2200,12 @@
         <v>76</v>
       </c>
       <c r="E40" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B41" t="s">
         <v>19</v>
@@ -2217,12 +2217,12 @@
         <v>71</v>
       </c>
       <c r="E41" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B42" t="s">
         <v>37</v>
@@ -2234,12 +2234,12 @@
         <v>59</v>
       </c>
       <c r="E42" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43" t="s">
         <v>33</v>
@@ -2251,12 +2251,12 @@
         <v>72</v>
       </c>
       <c r="E43" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
@@ -2268,12 +2268,12 @@
         <v>67</v>
       </c>
       <c r="E44" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
@@ -2285,12 +2285,12 @@
         <v>75</v>
       </c>
       <c r="E45" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
@@ -2302,12 +2302,12 @@
         <v>62</v>
       </c>
       <c r="E46" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B47" t="s">
         <v>6</v>
@@ -2319,12 +2319,12 @@
         <v>70</v>
       </c>
       <c r="E47" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B48" t="s">
         <v>27</v>
@@ -2336,12 +2336,12 @@
         <v>52</v>
       </c>
       <c r="E48" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B49" t="s">
         <v>37</v>
@@ -2353,12 +2353,12 @@
         <v>66</v>
       </c>
       <c r="E49" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B50" t="s">
         <v>22</v>
@@ -2370,12 +2370,12 @@
         <v>70</v>
       </c>
       <c r="E50" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B51" t="s">
         <v>33</v>
@@ -2387,12 +2387,12 @@
         <v>59</v>
       </c>
       <c r="E51" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B52" t="s">
         <v>27</v>
@@ -2404,15 +2404,15 @@
         <v>70</v>
       </c>
       <c r="E52" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C53">
         <v>36</v>
@@ -2421,12 +2421,12 @@
         <v>66</v>
       </c>
       <c r="E53" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B54" t="s">
         <v>27</v>
@@ -2438,12 +2438,12 @@
         <v>65</v>
       </c>
       <c r="E54" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
@@ -2455,12 +2455,12 @@
         <v>66</v>
       </c>
       <c r="E55" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
@@ -2472,12 +2472,12 @@
         <v>61</v>
       </c>
       <c r="E56" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" t="s">
         <v>10</v>
@@ -2489,12 +2489,12 @@
         <v>63</v>
       </c>
       <c r="E57" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
@@ -2506,12 +2506,12 @@
         <v>53</v>
       </c>
       <c r="E58" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
@@ -2523,12 +2523,12 @@
         <v>70</v>
       </c>
       <c r="E59" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B60" t="s">
         <v>19</v>
@@ -2540,12 +2540,12 @@
         <v>61</v>
       </c>
       <c r="E60" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B61" t="s">
         <v>22</v>
@@ -2557,12 +2557,12 @@
         <v>66</v>
       </c>
       <c r="E61" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B62" t="s">
         <v>37</v>
@@ -2574,15 +2574,15 @@
         <v>68</v>
       </c>
       <c r="E62" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C63">
         <v>48</v>
@@ -2591,12 +2591,12 @@
         <v>76</v>
       </c>
       <c r="E63" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B64" t="s">
         <v>27</v>
@@ -2608,12 +2608,12 @@
         <v>50</v>
       </c>
       <c r="E64" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="B65" t="s">
         <v>33</v>
@@ -2625,12 +2625,12 @@
         <v>63</v>
       </c>
       <c r="E65" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B66" t="s">
         <v>37</v>
@@ -2642,12 +2642,12 @@
         <v>56</v>
       </c>
       <c r="E66" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
@@ -2659,15 +2659,15 @@
         <v>64</v>
       </c>
       <c r="E67" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B68" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C68">
         <v>59</v>
@@ -2676,12 +2676,12 @@
         <v>58</v>
       </c>
       <c r="E68" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B69" t="s">
         <v>19</v>
@@ -2693,12 +2693,12 @@
         <v>74</v>
       </c>
       <c r="E69" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B70" t="s">
         <v>16</v>
@@ -2710,15 +2710,15 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B71" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C71">
         <v>65</v>
@@ -2727,12 +2727,12 @@
         <v>59</v>
       </c>
       <c r="E71" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B72" t="s">
         <v>27</v>
@@ -2744,12 +2744,12 @@
         <v>42</v>
       </c>
       <c r="E72" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B73" t="s">
         <v>19</v>
@@ -2761,12 +2761,12 @@
         <v>61</v>
       </c>
       <c r="E73" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B74" t="s">
         <v>33</v>
@@ -2778,12 +2778,12 @@
         <v>71</v>
       </c>
       <c r="E74" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B75" t="s">
         <v>14</v>
@@ -2795,15 +2795,15 @@
         <v>40</v>
       </c>
       <c r="E75" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B76" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C76">
         <v>69</v>
@@ -2812,12 +2812,12 @@
         <v>75</v>
       </c>
       <c r="E76" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B77" t="s">
         <v>10</v>
@@ -2829,12 +2829,12 @@
         <v>56</v>
       </c>
       <c r="E77" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B78" t="s">
         <v>33</v>
@@ -2846,12 +2846,12 @@
         <v>40</v>
       </c>
       <c r="E78" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
@@ -2863,12 +2863,12 @@
         <v>47</v>
       </c>
       <c r="E79" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B80" t="s">
         <v>16</v>
@@ -2880,12 +2880,12 @@
         <v>65</v>
       </c>
       <c r="E80" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B81" t="s">
         <v>37</v>
@@ -2897,15 +2897,15 @@
         <v>40</v>
       </c>
       <c r="E81" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B82" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C82">
         <v>66</v>
@@ -2914,12 +2914,12 @@
         <v>52</v>
       </c>
       <c r="E82" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B83" t="s">
         <v>37</v>
@@ -2931,12 +2931,12 @@
         <v>51</v>
       </c>
       <c r="E83" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B84" t="s">
         <v>6</v>
@@ -2948,12 +2948,12 @@
         <v>67</v>
       </c>
       <c r="E84" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B85" t="s">
         <v>33</v>
@@ -2965,12 +2965,12 @@
         <v>41</v>
       </c>
       <c r="E85" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B86" t="s">
         <v>6</v>
@@ -2982,12 +2982,12 @@
         <v>40</v>
       </c>
       <c r="E86" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B87" t="s">
         <v>12</v>
@@ -2999,12 +2999,12 @@
         <v>40</v>
       </c>
       <c r="E87" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B88" t="s">
         <v>27</v>
@@ -3016,12 +3016,12 @@
         <v>45</v>
       </c>
       <c r="E88" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B89" t="s">
         <v>14</v>
@@ -3033,12 +3033,12 @@
         <v>70</v>
       </c>
       <c r="E89" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B90" t="s">
         <v>8</v>
@@ -3050,32 +3050,32 @@
         <v>40</v>
       </c>
       <c r="E90" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B91" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C91">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D91">
         <v>39</v>
       </c>
       <c r="E91" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B92" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C92">
         <v>36</v>
@@ -3084,12 +3084,12 @@
         <v>63</v>
       </c>
       <c r="E92" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B93" t="s">
         <v>27</v>
@@ -3101,12 +3101,12 @@
         <v>40</v>
       </c>
       <c r="E93" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B94" t="s">
         <v>37</v>
@@ -3118,12 +3118,12 @@
         <v>53</v>
       </c>
       <c r="E94" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B95" t="s">
         <v>37</v>
@@ -3135,49 +3135,49 @@
         <v>51</v>
       </c>
       <c r="E95" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B96" t="s">
         <v>12</v>
       </c>
       <c r="C96">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D96">
         <v>42</v>
       </c>
       <c r="E96" t="s">
-        <v>316</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B97" t="s">
         <v>10</v>
       </c>
       <c r="C97">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D97">
         <v>40</v>
       </c>
       <c r="E97" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="B98" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C98">
         <v>82</v>
@@ -3186,12 +3186,12 @@
         <v>39</v>
       </c>
       <c r="E98" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B99" t="s">
         <v>8</v>
@@ -3203,12 +3203,12 @@
         <v>68</v>
       </c>
       <c r="E99" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B100" t="s">
         <v>27</v>
@@ -3220,12 +3220,12 @@
         <v>40</v>
       </c>
       <c r="E100" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B101" t="s">
         <v>6</v>
@@ -3237,12 +3237,12 @@
         <v>40</v>
       </c>
       <c r="E101" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B102" t="s">
         <v>14</v>
@@ -3254,12 +3254,12 @@
         <v>39</v>
       </c>
       <c r="E102" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B103" t="s">
         <v>19</v>
@@ -3271,12 +3271,12 @@
         <v>66</v>
       </c>
       <c r="E103" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B104" t="s">
         <v>12</v>
@@ -3288,12 +3288,12 @@
         <v>40</v>
       </c>
       <c r="E104" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B105" t="s">
         <v>33</v>
@@ -3305,12 +3305,12 @@
         <v>41</v>
       </c>
       <c r="E105" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B106" t="s">
         <v>27</v>
@@ -3322,12 +3322,12 @@
         <v>70</v>
       </c>
       <c r="E106" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B107" t="s">
         <v>33</v>
@@ -3339,12 +3339,12 @@
         <v>40</v>
       </c>
       <c r="E107" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B108" t="s">
         <v>14</v>
@@ -3356,12 +3356,12 @@
         <v>39</v>
       </c>
       <c r="E108" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B109" t="s">
         <v>8</v>
@@ -3373,12 +3373,12 @@
         <v>69</v>
       </c>
       <c r="E109" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B110" t="s">
         <v>33</v>
@@ -3390,12 +3390,12 @@
         <v>35</v>
       </c>
       <c r="E110" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B111" t="s">
         <v>12</v>
@@ -3407,12 +3407,12 @@
         <v>43</v>
       </c>
       <c r="E111" t="s">
-        <v>322</v>
+        <v>369</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B112" t="s">
         <v>8</v>
@@ -3424,12 +3424,12 @@
         <v>69</v>
       </c>
       <c r="E112" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B113" t="s">
         <v>16</v>
@@ -3441,12 +3441,12 @@
         <v>39</v>
       </c>
       <c r="E113" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B114" t="s">
         <v>22</v>
@@ -3458,12 +3458,12 @@
         <v>40</v>
       </c>
       <c r="E114" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B115" t="s">
         <v>6</v>
@@ -3475,12 +3475,12 @@
         <v>52</v>
       </c>
       <c r="E115" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B116" t="s">
         <v>33</v>
@@ -3492,12 +3492,12 @@
         <v>79</v>
       </c>
       <c r="E116" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B117" t="s">
         <v>22</v>
@@ -3509,12 +3509,12 @@
         <v>68</v>
       </c>
       <c r="E117" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B118" t="s">
         <v>16</v>
@@ -3526,12 +3526,12 @@
         <v>39</v>
       </c>
       <c r="E118" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B119" t="s">
         <v>16</v>
@@ -3543,12 +3543,12 @@
         <v>40</v>
       </c>
       <c r="E119" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B120" t="s">
         <v>19</v>
@@ -3560,12 +3560,12 @@
         <v>40</v>
       </c>
       <c r="E120" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B121" t="s">
         <v>27</v>
@@ -3577,12 +3577,12 @@
         <v>41</v>
       </c>
       <c r="E121" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="B122" t="s">
         <v>27</v>
@@ -3594,12 +3594,12 @@
         <v>40</v>
       </c>
       <c r="E122" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="B123" t="s">
         <v>16</v>
@@ -3611,12 +3611,12 @@
         <v>39</v>
       </c>
       <c r="E123" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B124" t="s">
         <v>33</v>
@@ -3628,12 +3628,12 @@
         <v>40</v>
       </c>
       <c r="E124" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B125" t="s">
         <v>14</v>
@@ -3645,12 +3645,12 @@
         <v>39</v>
       </c>
       <c r="E125" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B126" t="s">
         <v>22</v>
@@ -3662,12 +3662,12 @@
         <v>39</v>
       </c>
       <c r="E126" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B127" t="s">
         <v>19</v>
@@ -3679,12 +3679,12 @@
         <v>40</v>
       </c>
       <c r="E127" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B128" t="s">
         <v>6</v>
@@ -3696,12 +3696,12 @@
         <v>40</v>
       </c>
       <c r="E128" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B129" t="s">
         <v>22</v>
@@ -3713,29 +3713,29 @@
         <v>40</v>
       </c>
       <c r="E129" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B130" t="s">
         <v>8</v>
       </c>
       <c r="C130">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D130">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E130" t="s">
-        <v>211</v>
+        <v>368</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B131" t="s">
         <v>22</v>
@@ -3747,12 +3747,12 @@
         <v>47</v>
       </c>
       <c r="E131" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B132" t="s">
         <v>6</v>
@@ -3764,12 +3764,12 @@
         <v>65</v>
       </c>
       <c r="E132" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="B133" t="s">
         <v>22</v>
@@ -3781,12 +3781,12 @@
         <v>40</v>
       </c>
       <c r="E133" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B134" t="s">
         <v>6</v>
@@ -3798,12 +3798,12 @@
         <v>41</v>
       </c>
       <c r="E134" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B135" t="s">
         <v>22</v>
@@ -3815,15 +3815,15 @@
         <v>40</v>
       </c>
       <c r="E135" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B136" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C136">
         <v>59</v>
@@ -3832,12 +3832,12 @@
         <v>69</v>
       </c>
       <c r="E136" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B137" t="s">
         <v>19</v>
@@ -3849,12 +3849,12 @@
         <v>41</v>
       </c>
       <c r="E137" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B138" t="s">
         <v>22</v>
@@ -3866,15 +3866,15 @@
         <v>64</v>
       </c>
       <c r="E138" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B139" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C139">
         <v>49</v>
@@ -3883,15 +3883,15 @@
         <v>42</v>
       </c>
       <c r="E139" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B140" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C140">
         <v>50</v>
@@ -3900,12 +3900,12 @@
         <v>40</v>
       </c>
       <c r="E140" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B141" t="s">
         <v>27</v>
@@ -3917,12 +3917,12 @@
         <v>40</v>
       </c>
       <c r="E141" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B142" t="s">
         <v>16</v>
@@ -3934,12 +3934,12 @@
         <v>39</v>
       </c>
       <c r="E142" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B143" t="s">
         <v>6</v>
@@ -3951,12 +3951,12 @@
         <v>63</v>
       </c>
       <c r="E143" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B144" t="s">
         <v>10</v>
@@ -3968,12 +3968,12 @@
         <v>40</v>
       </c>
       <c r="E144" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B145" t="s">
         <v>10</v>
@@ -3985,12 +3985,12 @@
         <v>39</v>
       </c>
       <c r="E145" t="s">
-        <v>227</v>
+        <v>362</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B146" t="s">
         <v>8</v>
@@ -4002,12 +4002,12 @@
         <v>42</v>
       </c>
       <c r="E146" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B147" t="s">
         <v>27</v>
@@ -4019,12 +4019,12 @@
         <v>40</v>
       </c>
       <c r="E147" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B148" t="s">
         <v>37</v>
@@ -4036,12 +4036,12 @@
         <v>40</v>
       </c>
       <c r="E148" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B149" t="s">
         <v>16</v>
@@ -4053,12 +4053,12 @@
         <v>66</v>
       </c>
       <c r="E149" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B150" t="s">
         <v>6</v>
@@ -4070,12 +4070,12 @@
         <v>55</v>
       </c>
       <c r="E150" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B151" t="s">
         <v>27</v>
@@ -4087,12 +4087,12 @@
         <v>61</v>
       </c>
       <c r="E151" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B152" t="s">
         <v>10</v>
@@ -4104,12 +4104,12 @@
         <v>39</v>
       </c>
       <c r="E152" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B153" t="s">
         <v>14</v>
@@ -4121,12 +4121,12 @@
         <v>66</v>
       </c>
       <c r="E153" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B154" t="s">
         <v>33</v>
@@ -4138,12 +4138,12 @@
         <v>40</v>
       </c>
       <c r="E154" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B155" t="s">
         <v>14</v>
@@ -4155,15 +4155,15 @@
         <v>44</v>
       </c>
       <c r="E155" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B156" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C156">
         <v>30</v>
@@ -4172,12 +4172,12 @@
         <v>66</v>
       </c>
       <c r="E156" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B157" t="s">
         <v>12</v>
@@ -4189,12 +4189,12 @@
         <v>45</v>
       </c>
       <c r="E157" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B158" t="s">
         <v>19</v>
@@ -4206,15 +4206,15 @@
         <v>39</v>
       </c>
       <c r="E158" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B159" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C159">
         <v>73</v>
@@ -4223,12 +4223,12 @@
         <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B160" t="s">
         <v>22</v>
@@ -4240,12 +4240,12 @@
         <v>40</v>
       </c>
       <c r="E160" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B161" t="s">
         <v>33</v>
@@ -4257,12 +4257,12 @@
         <v>41</v>
       </c>
       <c r="E161" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B162" t="s">
         <v>37</v>
@@ -4274,12 +4274,12 @@
         <v>39</v>
       </c>
       <c r="E162" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B163" t="s">
         <v>12</v>
@@ -4291,12 +4291,12 @@
         <v>42</v>
       </c>
       <c r="E163" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B164" t="s">
         <v>27</v>
@@ -4308,12 +4308,12 @@
         <v>42</v>
       </c>
       <c r="E164" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B165" t="s">
         <v>12</v>
@@ -4325,15 +4325,15 @@
         <v>39</v>
       </c>
       <c r="E165" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B166" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C166">
         <v>45</v>
@@ -4342,12 +4342,12 @@
         <v>38</v>
       </c>
       <c r="E166" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B167" t="s">
         <v>37</v>
@@ -4359,12 +4359,12 @@
         <v>41</v>
       </c>
       <c r="E167" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B168" t="s">
         <v>19</v>
@@ -4376,12 +4376,12 @@
         <v>42</v>
       </c>
       <c r="E168" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B169" t="s">
         <v>10</v>
@@ -4393,12 +4393,12 @@
         <v>38</v>
       </c>
       <c r="E169" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B170" t="s">
         <v>8</v>
@@ -4410,12 +4410,12 @@
         <v>40</v>
       </c>
       <c r="E170" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B171" t="s">
         <v>33</v>
@@ -4427,12 +4427,12 @@
         <v>67</v>
       </c>
       <c r="E171" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B172" t="s">
         <v>14</v>
@@ -4444,12 +4444,12 @@
         <v>40</v>
       </c>
       <c r="E172" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B173" t="s">
         <v>14</v>
@@ -4461,12 +4461,12 @@
         <v>67</v>
       </c>
       <c r="E173" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B174" t="s">
         <v>14</v>
@@ -4478,12 +4478,12 @@
         <v>62</v>
       </c>
       <c r="E174" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B175" t="s">
         <v>37</v>
@@ -4495,12 +4495,12 @@
         <v>47</v>
       </c>
       <c r="E175" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B176" t="s">
         <v>22</v>
@@ -4512,12 +4512,12 @@
         <v>59</v>
       </c>
       <c r="E176" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B177" t="s">
         <v>14</v>
@@ -4529,12 +4529,12 @@
         <v>57</v>
       </c>
       <c r="E177" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B178" t="s">
         <v>33</v>
@@ -4546,7 +4546,7 @@
         <v>49</v>
       </c>
       <c r="E178" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/投手能力データ_最新.xlsx
+++ b/投手能力データ_最新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TakahisaFuji\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD9F956-2CCD-4F04-BD4E-86A3E72D340B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3F991D-3F05-47A5-849B-4E0972535A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="389">
   <si>
     <t>選手名</t>
   </si>
@@ -1173,6 +1173,130 @@
   </si>
   <si>
     <t>シンカー:F / カットボール:B / フォーク:C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山本由伸</t>
+    <rPh sb="0" eb="2">
+      <t>ヤマモト</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヨシノブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>千賀滉大</t>
+    <rPh sb="0" eb="2">
+      <t>センガ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今永昇太</t>
+    <rPh sb="0" eb="2">
+      <t>イマナガ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>菊池雄星</t>
+    <rPh sb="0" eb="4">
+      <t>キクチユウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>佐々木朗希</t>
+    <rPh sb="0" eb="3">
+      <t>ササキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ロウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MLB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今井達也</t>
+    <rPh sb="0" eb="2">
+      <t>イマイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タツヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>菅野智之</t>
+    <rPh sb="0" eb="4">
+      <t>スガノトモユキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダルビッシュ有</t>
+    <rPh sb="6" eb="7">
+      <t>ユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フォーシーム:A / スプリット:A / カットボール:A / カーブ:A / シンカー:B / スライダー:D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フォーシーム:B / フォーク:S / カットボール:C / スイーパー:C / スライダー:D / シンカー:D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フォーシーム:B / スプリット:A / スイーパー:D / シンカー:C / カーブ:D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フォーシーム:B / スライダー:B / スプリット:B / カーブ:B / カットボール:C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フォーシーム:B / スプリット:S / スライダー:D / フォーク:C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スライダー:A / フォーシーム:A / シンカー:E / スプリット:E / チェンジアップ:E</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スプリット:B / フォーシーム:D / シンカー:B / スイーパー:C / カットボール:C / スライダー:E / カーブ:D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シンカー:C / カーブ:C / フォーシーム:C / スライダー:C / カットボール:C / スプリット:D / スイーパー:F / チェンジアップ:E</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>松井裕樹</t>
+    <rPh sb="0" eb="2">
+      <t>マツイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ユウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フォーシーム:A / スライダー:S / スプリット:B / スイーパー:C / シンカー:B</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1557,9 +1681,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA75188-3E41-D340-AF95-7FD878AE408B}">
-  <dimension ref="A1:E178"/>
+  <dimension ref="A1:E187"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
+    <col min="1" max="1" width="13.25" customWidth="1"/>
     <col min="5" max="5" width="104" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4587,6 +4712,159 @@
       </c>
       <c r="E178" t="s">
         <v>303</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A179" t="s">
+        <v>370</v>
+      </c>
+      <c r="B179" t="s">
+        <v>375</v>
+      </c>
+      <c r="C179">
+        <v>91</v>
+      </c>
+      <c r="D179">
+        <v>93</v>
+      </c>
+      <c r="E179" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A180" t="s">
+        <v>371</v>
+      </c>
+      <c r="B180" t="s">
+        <v>375</v>
+      </c>
+      <c r="C180">
+        <v>58</v>
+      </c>
+      <c r="D180">
+        <v>82</v>
+      </c>
+      <c r="E180" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A181" t="s">
+        <v>372</v>
+      </c>
+      <c r="B181" t="s">
+        <v>375</v>
+      </c>
+      <c r="C181">
+        <v>78</v>
+      </c>
+      <c r="D181">
+        <v>80</v>
+      </c>
+      <c r="E181" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A182" t="s">
+        <v>373</v>
+      </c>
+      <c r="B182" t="s">
+        <v>375</v>
+      </c>
+      <c r="C182">
+        <v>57</v>
+      </c>
+      <c r="D182">
+        <v>85</v>
+      </c>
+      <c r="E182" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A183" t="s">
+        <v>374</v>
+      </c>
+      <c r="B183" t="s">
+        <v>375</v>
+      </c>
+      <c r="C183">
+        <v>75</v>
+      </c>
+      <c r="D183">
+        <v>71</v>
+      </c>
+      <c r="E183" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A184" t="s">
+        <v>376</v>
+      </c>
+      <c r="B184" t="s">
+        <v>375</v>
+      </c>
+      <c r="C184">
+        <v>63</v>
+      </c>
+      <c r="D184">
+        <v>88</v>
+      </c>
+      <c r="E184" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A185" t="s">
+        <v>377</v>
+      </c>
+      <c r="B185" t="s">
+        <v>375</v>
+      </c>
+      <c r="C185">
+        <v>78</v>
+      </c>
+      <c r="D185">
+        <v>82</v>
+      </c>
+      <c r="E185" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A186" t="s">
+        <v>378</v>
+      </c>
+      <c r="B186" t="s">
+        <v>375</v>
+      </c>
+      <c r="C186">
+        <v>84</v>
+      </c>
+      <c r="D186">
+        <v>75</v>
+      </c>
+      <c r="E186" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A187" t="s">
+        <v>387</v>
+      </c>
+      <c r="B187" t="s">
+        <v>375</v>
+      </c>
+      <c r="C187">
+        <v>48</v>
+      </c>
+      <c r="D187">
+        <v>49</v>
+      </c>
+      <c r="E187" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/投手能力データ_最新.xlsx
+++ b/投手能力データ_最新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TakahisaFuji\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B5C4FD-288D-45A0-94B6-692B05120440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8352996C-A0AB-4E10-B404-D27D16AF5A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3547,7 +3547,7 @@
         <v>68</v>
       </c>
       <c r="C60">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D60">
         <v>53</v>
@@ -3692,7 +3692,7 @@
         <v>68</v>
       </c>
       <c r="C65">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D65">
         <v>57</v>
@@ -3701,7 +3701,7 @@
         <v>72</v>
       </c>
       <c r="F65">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I65">
         <v>71</v>
@@ -3710,10 +3710,10 @@
         <v>67</v>
       </c>
       <c r="K65">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="L65">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.15">
@@ -4549,10 +4549,10 @@
         <v>110</v>
       </c>
       <c r="C93">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D93">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E93">
         <v>40</v>
@@ -4564,7 +4564,7 @@
         <v>77</v>
       </c>
       <c r="I93">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="M93">
         <v>65</v>
@@ -4755,7 +4755,7 @@
         <v>110</v>
       </c>
       <c r="C100">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D100">
         <v>51</v>
@@ -4764,10 +4764,10 @@
         <v>44</v>
       </c>
       <c r="F100">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H100">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I100">
         <v>70</v>
@@ -7007,19 +7007,19 @@
         <v>48</v>
       </c>
       <c r="F173">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H173">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="I173">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="J173">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K173">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.15">
@@ -7611,22 +7611,22 @@
         <v>199</v>
       </c>
       <c r="C193">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D193">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E193">
         <v>73</v>
       </c>
       <c r="F193">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G193">
         <v>78</v>
       </c>
       <c r="H193">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="I193">
         <v>65</v>
@@ -7635,10 +7635,10 @@
         <v>38</v>
       </c>
       <c r="K193">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="L193">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="M193">
         <v>65</v>
@@ -9040,16 +9040,16 @@
         <v>41</v>
       </c>
       <c r="D240">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="E240">
         <v>38</v>
       </c>
       <c r="F240">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H240">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="L240">
         <v>67</v>

--- a/投手能力データ_最新.xlsx
+++ b/投手能力データ_最新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TakahisaFuji\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8352996C-A0AB-4E10-B404-D27D16AF5A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95CE93D6-4517-463A-B479-25C9998F5739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3724,7 +3724,7 @@
         <v>68</v>
       </c>
       <c r="C66">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D66">
         <v>77</v>
@@ -3736,13 +3736,13 @@
         <v>85</v>
       </c>
       <c r="H66">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I66">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="L66">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.15">

--- a/投手能力データ_最新.xlsx
+++ b/投手能力データ_最新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TakahisaFuji\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95CE93D6-4517-463A-B479-25C9998F5739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8CBD6D-35CA-4E01-8E3D-64212E9D0B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1924,7 +1924,7 @@
         <v>37</v>
       </c>
       <c r="F6">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H6">
         <v>57</v>
@@ -2072,10 +2072,10 @@
         <v>82</v>
       </c>
       <c r="H11">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="I11">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="J11">
         <v>45</v>
@@ -2185,13 +2185,13 @@
         <v>84</v>
       </c>
       <c r="E15">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F15">
         <v>67</v>
       </c>
       <c r="G15">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H15">
         <v>72</v>
@@ -2359,16 +2359,16 @@
         <v>17</v>
       </c>
       <c r="C21">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D21">
         <v>70</v>
       </c>
       <c r="E21">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F21">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="G21">
         <v>81</v>
@@ -2377,7 +2377,7 @@
         <v>37</v>
       </c>
       <c r="J21">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="K21">
         <v>63</v>
@@ -3927,7 +3927,7 @@
         <v>87</v>
       </c>
       <c r="C73">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D73">
         <v>74</v>
@@ -4113,25 +4113,25 @@
         <v>87</v>
       </c>
       <c r="C79">
+        <v>76</v>
+      </c>
+      <c r="D79">
+        <v>76</v>
+      </c>
+      <c r="E79">
         <v>80</v>
-      </c>
-      <c r="D79">
-        <v>82</v>
-      </c>
-      <c r="E79">
-        <v>77</v>
       </c>
       <c r="F79">
         <v>71</v>
       </c>
       <c r="G79">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H79">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="I79">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="J79">
         <v>59</v>
@@ -5072,7 +5072,7 @@
         <v>63</v>
       </c>
       <c r="G110">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I110">
         <v>59</v>
@@ -5362,7 +5362,7 @@
         <v>71</v>
       </c>
       <c r="D120">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E120">
         <v>32</v>
@@ -5371,10 +5371,10 @@
         <v>60</v>
       </c>
       <c r="H120">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="I120">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.15">
@@ -5580,7 +5580,7 @@
         <v>129</v>
       </c>
       <c r="C127">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D127">
         <v>49</v>
@@ -5818,10 +5818,10 @@
         <v>150</v>
       </c>
       <c r="C135">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D135">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E135">
         <v>79</v>
@@ -5830,16 +5830,16 @@
         <v>80</v>
       </c>
       <c r="G135">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H135">
         <v>68</v>
       </c>
       <c r="I135">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J135">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="L135">
         <v>55</v>
@@ -6001,7 +6001,7 @@
         <v>150</v>
       </c>
       <c r="C141">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D141">
         <v>69</v>
@@ -6019,7 +6019,7 @@
         <v>46</v>
       </c>
       <c r="K141">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="L141">
         <v>76</v>
@@ -6164,10 +6164,10 @@
         <v>150</v>
       </c>
       <c r="C146">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="D146">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E146">
         <v>34</v>
@@ -6228,7 +6228,7 @@
         <v>150</v>
       </c>
       <c r="C148">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D148">
         <v>63</v>
@@ -6237,7 +6237,7 @@
         <v>73</v>
       </c>
       <c r="F148">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G148">
         <v>62</v>
@@ -6246,10 +6246,10 @@
         <v>44</v>
       </c>
       <c r="I148">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="J148">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="K148">
         <v>78</v>
@@ -9266,7 +9266,7 @@
         <v>267</v>
       </c>
       <c r="C248">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D248">
         <v>86</v>
@@ -9275,7 +9275,7 @@
         <v>61</v>
       </c>
       <c r="F248">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G248">
         <v>78</v>
@@ -9287,7 +9287,7 @@
         <v>49</v>
       </c>
       <c r="K248">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.15">
@@ -9379,10 +9379,10 @@
         <v>267</v>
       </c>
       <c r="C252">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D252">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E252">
         <v>81</v>
@@ -9391,13 +9391,13 @@
         <v>76</v>
       </c>
       <c r="H252">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="I252">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="L252">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.15">
@@ -9458,13 +9458,13 @@
         <v>77</v>
       </c>
       <c r="I254">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="J254">
         <v>75</v>
       </c>
       <c r="L254">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.15">
@@ -9608,10 +9608,10 @@
         <v>267</v>
       </c>
       <c r="C260">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D260">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E260">
         <v>54</v>
@@ -9623,7 +9623,7 @@
         <v>49</v>
       </c>
       <c r="I260">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K260">
         <v>44</v>
@@ -9666,13 +9666,13 @@
         <v>267</v>
       </c>
       <c r="C262">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D262">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E262">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F262">
         <v>72</v>
@@ -9684,10 +9684,10 @@
         <v>82</v>
       </c>
       <c r="I262">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="J262">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K262">
         <v>55</v>

--- a/投手能力データ_最新.xlsx
+++ b/投手能力データ_最新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TakahisaFuji\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8CBD6D-35CA-4E01-8E3D-64212E9D0B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3614A58A-CA90-49E1-9C0F-8D8154F25631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3282,16 +3282,16 @@
         <v>68</v>
       </c>
       <c r="C52">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D52">
         <v>24</v>
       </c>
       <c r="E52">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F52">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H52">
         <v>71</v>
@@ -3340,7 +3340,7 @@
         <v>68</v>
       </c>
       <c r="C54">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D54">
         <v>76</v>
@@ -3692,7 +3692,7 @@
         <v>68</v>
       </c>
       <c r="C65">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D65">
         <v>57</v>
@@ -4113,7 +4113,7 @@
         <v>87</v>
       </c>
       <c r="C79">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D79">
         <v>76</v>
@@ -4128,13 +4128,13 @@
         <v>55</v>
       </c>
       <c r="H79">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="I79">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J79">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="K79">
         <v>58</v>
@@ -5420,7 +5420,7 @@
         <v>129</v>
       </c>
       <c r="C122">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D122">
         <v>78</v>
@@ -5429,16 +5429,16 @@
         <v>56</v>
       </c>
       <c r="F122">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="G122">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="H122">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="I122">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="K122">
         <v>61</v>
@@ -6658,7 +6658,7 @@
         <v>175</v>
       </c>
       <c r="C162">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D162">
         <v>84</v>
@@ -6667,7 +6667,7 @@
         <v>77</v>
       </c>
       <c r="F162">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H162">
         <v>81</v>
@@ -6676,10 +6676,10 @@
         <v>33</v>
       </c>
       <c r="J162">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="L162">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.15">
@@ -6743,7 +6743,7 @@
         <v>97</v>
       </c>
       <c r="L164">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.15">
@@ -6934,7 +6934,7 @@
         <v>175</v>
       </c>
       <c r="C171">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D171">
         <v>78</v>
@@ -6943,7 +6943,7 @@
         <v>45</v>
       </c>
       <c r="F171">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I171">
         <v>56</v>
@@ -7111,7 +7111,7 @@
         <v>199</v>
       </c>
       <c r="C177">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D177">
         <v>56</v>
@@ -7120,7 +7120,7 @@
         <v>88</v>
       </c>
       <c r="F177">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="G177">
         <v>57</v>
@@ -7129,7 +7129,7 @@
         <v>48</v>
       </c>
       <c r="I177">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="J177">
         <v>49</v>
@@ -7138,10 +7138,10 @@
         <v>44</v>
       </c>
       <c r="L177">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="M177">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.15">
@@ -7190,7 +7190,7 @@
         <v>199</v>
       </c>
       <c r="C179">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D179">
         <v>69</v>
@@ -7202,7 +7202,7 @@
         <v>79</v>
       </c>
       <c r="H179">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="J179">
         <v>69</v>
@@ -7309,7 +7309,7 @@
         <v>199</v>
       </c>
       <c r="C183">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D183">
         <v>60</v>
@@ -7324,16 +7324,16 @@
         <v>60</v>
       </c>
       <c r="H183">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="I183">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J183">
         <v>37</v>
       </c>
       <c r="K183">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L183">
         <v>39</v>
@@ -7515,7 +7515,7 @@
         <v>199</v>
       </c>
       <c r="C190">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D190">
         <v>55</v>
@@ -7524,7 +7524,7 @@
         <v>57</v>
       </c>
       <c r="F190">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G190">
         <v>37</v>
@@ -7536,7 +7536,7 @@
         <v>68</v>
       </c>
       <c r="J190">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L190">
         <v>73</v>
@@ -7576,7 +7576,7 @@
         <v>199</v>
       </c>
       <c r="C192">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D192">
         <v>45</v>
@@ -7591,16 +7591,16 @@
         <v>63</v>
       </c>
       <c r="H192">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="I192">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="J192">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="M192">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.15">
@@ -9394,7 +9394,7 @@
         <v>84</v>
       </c>
       <c r="I252">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="L252">
         <v>68</v>
@@ -9545,7 +9545,7 @@
         <v>30</v>
       </c>
       <c r="J257">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="K257">
         <v>54</v>
@@ -9611,13 +9611,13 @@
         <v>41</v>
       </c>
       <c r="D260">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E260">
         <v>54</v>
       </c>
       <c r="F260">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G260">
         <v>49</v>
@@ -9666,10 +9666,10 @@
         <v>267</v>
       </c>
       <c r="C262">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D262">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E262">
         <v>78</v>
@@ -9681,7 +9681,7 @@
         <v>95</v>
       </c>
       <c r="H262">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I262">
         <v>59</v>
@@ -9690,10 +9690,10 @@
         <v>66</v>
       </c>
       <c r="K262">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="L262">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/投手能力データ_最新.xlsx
+++ b/投手能力データ_最新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TakahisaFuji\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3AA6EEE-372F-C24C-A206-2339D58ACD11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D2A4D70-8931-FF4F-AA30-50D2E4CBEE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5670,7 +5670,7 @@
         <v>150</v>
       </c>
       <c r="C130">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D130">
         <v>58</v>
@@ -5679,16 +5679,16 @@
         <v>55</v>
       </c>
       <c r="F130">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I130">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="K130">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="L130">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.1">
@@ -82189,20 +82189,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -82219,6 +82219,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CA221B6-A047-4ED6-B0AC-3DFD3F306189}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26B35F0A-2F11-4BAB-8A20-5EA556DD7198}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -82227,12 +82235,4 @@
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CA221B6-A047-4ED6-B0AC-3DFD3F306189}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>